--- a/output/pdf_financials_xlsx/ELR.xlsx
+++ b/output/pdf_financials_xlsx/ELR.xlsx
@@ -2148,19 +2148,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.154</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0.144</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.151</v>
+        <v>2.636</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>7.089</v>
@@ -2208,19 +2208,19 @@
         <v>-143.774</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-22.921</v>
+        <v>-24.075</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-54.692</v>
+        <v>-54.964</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.776999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-25.814</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.773</v>
+        <v>1.712</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>4.503</v>
@@ -2300,7 +2300,7 @@
         <v>-6235.265700483092</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1.969828245247439</v>
+        <v>4.362672646654095</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>6.602832927651837</v>
@@ -5852,19 +5852,19 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>17.456</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-103.479</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-128.768</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-208.42</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-244.432</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>-308.468</v>
@@ -6344,13 +6344,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.154</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0.144</v>
@@ -21063,7 +21063,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -24615,7 +24619,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -39841,7 +39849,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -61090,7 +61098,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -65472,7 +65480,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -75685,7 +75693,7 @@
         <v>-213.116</v>
       </c>
       <c r="F679" s="5" t="n">
-        <v>1.222</v>
+        <v>-1.222</v>
       </c>
       <c r="G679" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ELR.xlsx
+++ b/output/pdf_financials_xlsx/ELR.xlsx
@@ -1092,37 +1092,37 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>5.529</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3.407</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2.137</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.091</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.195</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.801</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.161</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.108</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.708</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.306</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="13">
@@ -2076,37 +2076,37 @@
         <v>9.776999999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-86.932</v>
+        <v>-92.461</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-127.91</v>
+        <v>-131.317</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-180.573</v>
+        <v>-182.71</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-143.774</v>
+        <v>-145.865</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-24.075</v>
+        <v>-25.27</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-54.964</v>
+        <v>-55.765</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-8.9</v>
+        <v>-10.061</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-25.958</v>
+        <v>-27.066</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.924</v>
+        <v>-1.632</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.586</v>
+        <v>-2.953</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.016</v>
+        <v>-3.496</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-12.715</v>
+        <v>-14.021</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-19.181</v>
+        <v>-19.66</v>
       </c>
     </row>
     <row r="28">
@@ -2148,19 +2148,19 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0.144</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>2.636</v>
+        <v>0.151</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>7.089</v>
@@ -2196,37 +2196,37 @@
         <v>32.284</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-65.762</v>
+        <v>-71.291</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-114.135</v>
+        <v>-117.542</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-174.455</v>
+        <v>-176.592</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-143.774</v>
+        <v>-145.865</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-24.075</v>
+        <v>-24.116</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-54.964</v>
+        <v>-55.493</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.9</v>
+        <v>-9.938000000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-25.814</v>
+        <v>-26.922</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.712</v>
+        <v>-1.481</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>4.503</v>
+        <v>4.136</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.289</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-7.998</v>
+        <v>-9.304</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-17.674</v>
+        <v>-18.153</v>
       </c>
     </row>
     <row r="30">
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6235.265700483092</v>
+        <v>-6502.898550724638</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.362672646654095</v>
+        <v>-3.774017634167474</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.602832927651837</v>
+        <v>6.06469397929558</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.392220180762021</v>
+        <v>1.501401184046917</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-12.79536691890508</v>
+        <v>-14.88473290991409</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-28.69808073263404</v>
+        <v>-29.47585490208814</v>
       </c>
     </row>
     <row r="31">
@@ -6344,13 +6344,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0.144</v>
@@ -7785,19 +7785,19 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-1.706</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-1.642</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-1.481</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="125">
@@ -7843,19 +7843,19 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-1.706</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-1.642</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-1.481</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="126">
@@ -32028,7 +32028,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -36599,7 +36603,11 @@
           <t>Lease payments 17</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -38484,7 +38492,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -39849,7 +39861,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -53464,7 +53476,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -56288,7 +56300,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -58019,7 +58031,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -61098,7 +61110,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -61593,7 +61605,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -65480,7 +65492,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -66979,7 +66991,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -69573,7 +69585,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELR.xlsx
+++ b/output/pdf_financials_xlsx/ELR.xlsx
@@ -1392,7 +1392,7 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.056</v>
+        <v>0.056</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-13.968</v>
@@ -1401,7 +1401,7 @@
         <v>0.358</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>11.114</v>
+        <v>-11.114</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.722</v>
@@ -1419,7 +1419,7 @@
         <v>0.222</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0.125</v>
+        <v>0.125</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-2.222</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0.068</v>
+        <v>0.068</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.795</v>
+        <v>-0.795</v>
       </c>
     </row>
     <row r="18">
@@ -2825,52 +2825,52 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>1.655</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>3.473</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>5.514</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>2.947</v>
       </c>
     </row>
     <row r="41">
@@ -2883,52 +2883,52 @@
         <v>32.56</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>29.138</v>
+        <v>29.212</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>33.787</v>
+        <v>33.981</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>23.58</v>
+        <v>24.108</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>15.556</v>
+        <v>16.144</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.608</v>
+        <v>4.085</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>3.227</v>
+        <v>4.644</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1.159</v>
+        <v>1.884</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.834</v>
+        <v>1.262</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.894</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>1.345</v>
+        <v>1.809</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.796</v>
+        <v>16.802</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>21.355</v>
+        <v>23.01</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>22.617</v>
+        <v>24.409</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>27.657</v>
+        <v>31.13</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>27.282</v>
+        <v>32.796</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>38.718</v>
+        <v>41.665</v>
       </c>
     </row>
     <row r="42">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.286</v>
+        <v>6.698</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.739</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -4425,28 +4425,28 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>6.849</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>10.24</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>20.464</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>8.055</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.433</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -4489,22 +4489,22 @@
         <v>27.009</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>40.459</v>
+        <v>60.923</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>17.879</v>
+        <v>25.934</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>6.086</v>
+        <v>7.519</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>5.078</v>
+        <v>5.565</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>3.615</v>
+        <v>4.027</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1.586</v>
+        <v>1.827</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>1.541</v>
@@ -4632,19 +4632,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>1.448</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="71">
@@ -4690,19 +4690,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>1.448</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="72">
@@ -4895,10 +4895,10 @@
         <v>3.211</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.675</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.741</v>
+        <v>15.686</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -4922,19 +4922,19 @@
         <v>0.018</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1.935</v>
+        <v>0.487</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>53.47</v>
+        <v>51.735</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>54.333</v>
+        <v>53.851</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>55.266</v>
+        <v>55.248</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>63.16</v>
+        <v>62.885</v>
       </c>
     </row>
     <row r="76">
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.02757831070401852</v>
+        <v>0.04559879531566961</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.005942866510922579</v>
+        <v>0.02964602374414252</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.0007186448411566759</v>
+        <v>0.006216848229053784</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.0005550892204381143</v>
+        <v>0.0007987869269719206</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.007590966122961104</v>
+        <v>0.01190401505646173</v>
       </c>
     </row>
     <row r="81">
@@ -9825,7 +9825,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12963,7 +12967,11 @@
           <t>Lease liabilities 17 482</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15720,7 +15728,11 @@
           <t>Lease liabilities 18</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -54084,7 +54096,11 @@
           <t>Income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -58619,7 +58635,11 @@
           <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -60815,7 +60835,11 @@
           <t>Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -67500,7 +67524,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -70082,7 +70110,11 @@
           <t>Income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -73500,7 +73532,11 @@
           <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E657" t="inlineStr">
         <is>
           <t>-</t>
